--- a/LLM_10samples.xlsx
+++ b/LLM_10samples.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="179">
   <si>
     <t>Article ID</t>
   </si>
@@ -49,331 +49,301 @@
     <t>001_c001</t>
   </si>
   <si>
-    <t>PENYAKIT: Gangguan Kebimbangan Sosial, Umum, Panik, gangguan kecemasan, kemurungan. GEJALA: Insomnia, sakit kepala, gastrik, hipertensi, pening, cirit-birit, ketidakselesaan dada, berdebar-debar, sakit dan sakit. PUNCA: Pelbagai faktor. RAWATAN: ubat, kaunseling, psikoterapi.</t>
-  </si>
-  <si>
-    <t>WRONG LABEL: "Mengelakkan situasi yang menakutkan" (Dilabel GEJALA, sepatutnya FAKTOR_RISIKO atau PENCEGAHAN).</t>
-  </si>
-  <si>
-    <t>"perhatian orang lain" (PUNCA/pencetus).</t>
-  </si>
-  <si>
-    <t>adaGejala: Gangguan Kebimbangan Sosial -&gt; Insomnia, sakit kepala, cirit-birit, pening, hipertensi. punca: gangguan kecemasan -&gt; Pelbagai faktor; kemurungan -&gt; Gangguan Kebimbangan Sosial. rawatanDgn: gangguan kecemasan -&gt; ubat, kaunseling.</t>
+    <t>PENYAKIT: Gangguan Kebimbangan Sosial, Gangguan Kebimbangan Umum, Gangguan Panik, gangguan kecemasan, kemurungan. GEJALA: Insomnia, sakit kepala, gastrik, hipertensi, pening, cirit-birit, ketidakselesaan dada, berdebar-debar, sakit dan sakit. PUNCA: Pelbagai faktor. RAWATAN: ubat, kaunseling, psikoterapi. 1-3</t>
+  </si>
+  <si>
+    <t>WRONG LABEL: "Mengelakkan situasi yang menakutkan" (Dilabel GEJALA, manakala teks merujuknya sebagai tingkah laku pencetus). 1</t>
+  </si>
+  <si>
+    <t>"perhatian orang lain" (PUNCA/Pencetus). 1</t>
+  </si>
+  <si>
+    <t>adaGejala: Gangguan Kebimbangan Sosial -&gt; Berlebihan..., Insomnia, sakit kepala, ketidakselesaan dada, berdebar-debar, sakit dan sakit, cirit-birit, gastrik, pening, hipertensi. punca: Pelbagai faktor -&gt; gangguan kecemasan, Gangguan Kebimbangan Sosial -&gt; kemurungan. 1-5</t>
+  </si>
+  <si>
+    <t>WRONG RELATION: "rawatanDgn" (Walaupun logik, ia tidak mematuhi skema label hubungan jika diminta strictly adaRawatan mengikut prompt sebelumnya, namun dibenarkan dalam Accepted Relation Types di sini).</t>
+  </si>
+  <si>
+    <t>Hubungan antara "perasaan takut" dengan punca.</t>
+  </si>
+  <si>
+    <t>NER sangat luas, namun kategori tingkah laku tersalah label sebagai gejala fizikal. 1-8</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>002_c001</t>
+  </si>
+  <si>
+    <t>PENYAKIT: Ulser peptik, Tumor benigna, Polip. GEJALA: najis gelap, Muntah darah, Muntah menyerupai serbuk kopi. RAWATAN: Endoskopi. 9-11</t>
+  </si>
+  <si>
+    <t>WRONG LABEL: "Pendarahan gastrousus" (Dilabel GEJALA, manakala ia adalah keadaan/PENYAKIT utama dalam konteks ini). 9, 10</t>
+  </si>
+  <si>
+    <t>"Penyakit Crohn", "Kolitis Ulseratif" (PENYAKIT). 9, 12</t>
+  </si>
+  <si>
+    <t>punca: Ulser peptik, Tumor benigna, Polip, Keradangan kolon -&gt; Pendarahan gastrousus. adaRisiko: penyalahgunaan alkohol, Gastroenteritis -&gt; Mallory-Weiss Syndrome. adaGejala: Pendarahan gastrousus -&gt; najis gelap, Muntah darah, dll. 9-12</t>
+  </si>
+  <si>
+    <t>rawatanDgn: Pendarahan gastrousus -&gt; Endoskopi. 11</t>
+  </si>
+  <si>
+    <t>Hubungan punca bagi "Pecah urat esofagus". 9</t>
+  </si>
+  <si>
+    <t>Hubungan etiologi dikesan dengan sangat baik. 9-12</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>002_c002</t>
+  </si>
+  <si>
+    <t>PENYAKIT: Buasir, Jangkitan. RAWATAN: ubat, pembedahan, antibiotik yang sesuai, Terapi perencat pam proton. 11, 13</t>
+  </si>
+  <si>
+    <t>WRONG LABEL: "pendarahan" (Dilabel PUNCA, manakala teks menyatakan pendarahan adalah kondisi yang dirawat). 11, 13</t>
+  </si>
+  <si>
+    <t>"asid gastrik" (PUNCA bagi lesi). 11</t>
+  </si>
+  <si>
+    <t>rawatanDgn: Buasir -&gt; ubat, pembedahan, Jangkitan -&gt; antibiotik. 13</t>
   </si>
   <si>
     <t>Tiada.</t>
   </si>
   <si>
-    <t>Hubungan antara "perasaan takut" dengan punca kebimbangan.</t>
-  </si>
-  <si>
-    <t>NER sangat komprehensif tetapi tersalah melabel tingkah laku sebagai gejala fizikal. 1, 2, 3, 4</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>002_c001</t>
-  </si>
-  <si>
-    <t>PENYAKIT: Ulser peptik, Tumor benigna, Polip. GEJALA: najis gelap, Muntah darah. PUNCA: penyalahgunaan alkohol, Gastroenteritis.</t>
-  </si>
-  <si>
-    <t>WRONG LABEL: "Pendarahan gastrousus" (Dilabel GEJALA, ia adalah PENYAKIT utama).</t>
-  </si>
-  <si>
-    <t>"Kolitis Ulseratif" (PENYAKIT).</t>
-  </si>
-  <si>
-    <t>punca: Ulser peptik, Polip -&gt; Pendarahan gastrousus. adaRisiko: penyalahgunaan alkohol -&gt; Mallory-Weiss Syndrome. adaGejala: Pendarahan gastrousus -&gt; najis gelap.</t>
-  </si>
-  <si>
-    <t>Hubungan punca bagi "Penyakit Crohn".</t>
-  </si>
-  <si>
-    <t>Mengenalpasti punca pendarahan dengan sangat baik. 5, 6, 7, 8</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>002_c002</t>
-  </si>
-  <si>
-    <t>PENYAKIT: Buasir, Jangkitan. RAWATAN: ubat, pembedahan, antibiotik yang sesuai, Terapi perencat pam proton.</t>
-  </si>
-  <si>
-    <t>WRONG LABEL: "pendarahan" (Dilabel PUNCA, ia adalah kondisi yang dirawat).</t>
-  </si>
-  <si>
-    <t>"asid gastrik" (PUNCA).</t>
-  </si>
-  <si>
-    <t>rawatanDgn: Buasir -&gt; ubat, pembedahan; Jangkitan -&gt; antibiotik.</t>
-  </si>
-  <si>
-    <t>rawatanDgn: Pendarahan -&gt; Terapi perencat pam proton.</t>
-  </si>
-  <si>
-    <t>RE bagi ubat-ubatan farmakologi adalah sangat jitu. 8, 9</t>
-  </si>
-  <si>
-    <t>004</t>
-  </si>
-  <si>
-    <t>004_c001</t>
-  </si>
-  <si>
-    <t>PENYAKIT: aneurisme otak. PUNCA: penuaan, tekanan darah tinggi, aterosklerosis, pengambilan alkohol, dadah, kecederaan kepala, jangkitan, tumor. RAWATAN: Prosedur Pintasan.</t>
-  </si>
-  <si>
-    <t>WRONG LABEL: "proses degenerasi" (Dilabel GEJALA, ia adalah PUNCA).</t>
-  </si>
-  <si>
-    <t>"wanita" (FAKTOR_RISIKO).</t>
-  </si>
-  <si>
-    <t>punca: peningkatan usia, tekanan darah tinggi, tumor -&gt; aneurisme otak. rawatanDgn: aneurisme otak -&gt; Prosedur Pintasan.</t>
-  </si>
-  <si>
-    <t>adaRisiko: wanita -&gt; aneurisme otak.</t>
-  </si>
-  <si>
-    <t>Kebanyakan faktor etiologi berjaya dikaitkan dengan tepat. 10, 11</t>
-  </si>
-  <si>
-    <t>004_c002</t>
-  </si>
-  <si>
-    <t>RAWATAN: Prosedur Endovaskular, Oklusi.</t>
-  </si>
-  <si>
-    <t>WRONG ENTITY: "Kateter dimasukkan...", "Keratan mikrosurgikal..." (Dilabel RAWATAN, ini adalah ayat penjelasan, bukan entiti).</t>
-  </si>
-  <si>
-    <t>"bekuan darah" (GEJALA).</t>
-  </si>
-  <si>
-    <t>rawatanDgn: aneurisme -&gt; Endovaskular.</t>
-  </si>
-  <si>
-    <t>WRONG RELATION: aneurisme -&gt; rawatanDgn -&gt; "Kateter dimasukkan..." (Menggunakan ayat penuh sebagai objek).</t>
-  </si>
-  <si>
-    <t>Sistem gagal mengekstrak entiti yang bersih; memasukkan seluruh huraian teks ke dalam slot entiti. 11</t>
+    <t>rawatanDgn: Pendarahan -&gt; Terapi perencat pam proton. 11</t>
+  </si>
+  <si>
+    <t>Pemetaan rawatan farmakologi adalah jitu. 11, 13</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>012_c001</t>
+  </si>
+  <si>
+    <t>PENYAKIT: Glaukoma. GEJALA: penglihatan kabur, sakit mata, sakit kepala, penglihatan yang lemah, buta, 'penglihatan terowong'. 14</t>
+  </si>
+  <si>
+    <t>WRONG LABEL: "Saraf optik" (Dilabel PENYAKIT, ia adalah ANATOMI). 14</t>
+  </si>
+  <si>
+    <t>"tekanan cecair yang tinggi" (PUNCA). 14</t>
+  </si>
+  <si>
+    <t>adaGejala: Glaukoma -&gt; penglihatan kabur, sakit mata, sakit kepala, buta, 'penglihatan terowong'. 14</t>
+  </si>
+  <si>
+    <t>punca: tekanan cecair tinggi -&gt; glaukoma (Kandungan subjek tiada dalam label NER chunk ini).</t>
+  </si>
+  <si>
+    <t>Melabel bahagian anatomi sebagai penyakit adalah ralat struktur NER. 14</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>014_c001</t>
+  </si>
+  <si>
+    <t>PENYAKIT: kehilangan pendengaran, otitis media, penyakit ménière. FAKTOR_RISIKO: umur lanjut. PUNCA: antibiotik, ubat kanser tertentu, otitis media, penyakit atau trauma kronik, jangkitan kuman, bunyi yang kuat. 15</t>
+  </si>
+  <si>
+    <t>WRONG ENTITY: "tekanan intraokular tinggi" (Dilabel PUNCA - HALUSINASI, teks tidak menyebut tekanan mata bagi pendengaran). 15</t>
+  </si>
+  <si>
+    <t>punca: antibiotik, ubat kanser, bunyi kuat -&gt; kehilangan pendengaran. 15</t>
+  </si>
+  <si>
+    <t>Tiada ramalan salah lain selain entiti halusinasi tersebut.</t>
+  </si>
+  <si>
+    <t>punca: otitis media -&gt; kehilangan pendengaran. 15</t>
+  </si>
+  <si>
+    <t>Isu halusinasi sistematik "tekanan mata" menjejaskan integriti data. 15</t>
+  </si>
+  <si>
+    <t>014_c002</t>
+  </si>
+  <si>
+    <t>PENYAKIT: saluran telinga luar tersumbat, jangkitan telinga, jangkitan telinga luar. PUNCA: lilin, objek asing, benda asing. RAWATAN: pembaikan pembedahan. 16, 17</t>
+  </si>
+  <si>
+    <t>"gegendang telinga pecah" (PENYAKIT). 17</t>
+  </si>
+  <si>
+    <t>adaGejala: saluran telinga tersumbat, jangkitan telinga -&gt; kehilangan pendengaran. punca: lilin, objek asing -&gt; saluran telinga tersumbat. 16, 17</t>
+  </si>
+  <si>
+    <t>rawatanDgn: gegendang telinga pecah -&gt; pembaikan pembedahan. (Tiada entiti subjek dalam NER).</t>
+  </si>
+  <si>
+    <t>adaGejala: jangkitan telinga luar -&gt; sakit telinga. 17</t>
+  </si>
+  <si>
+    <t>Membezakan antara punca fizikal dan jangkitan dengan baik. 16, 17</t>
+  </si>
+  <si>
+    <t>034</t>
+  </si>
+  <si>
+    <t>034_c001</t>
+  </si>
+  <si>
+    <t>PENYAKIT: penyakit seliak, CD. GEJALA: ketidakselesaan perut, kembung perut, cirit-birit, sembelit, hilang berat badan, anemia, kabut otak. PUNCA: kecenderungan genetik, gluten. DIAGNOSIS: ujian darah, biopsi usus kecil. 18-21</t>
+  </si>
+  <si>
+    <t>"protein khusus" (PUNCA). 19</t>
+  </si>
+  <si>
+    <t>adaGejala: penyakit seliak -&gt; ketidakselesaan perut, sembelit, anemia, kabut otak, dll. punca: kecenderungan genetik, gluten -&gt; penyakit seliak. 19-21</t>
+  </si>
+  <si>
+    <t>diagnoseOleh: penyakit seliak -&gt; biopsi usus kecil. 21</t>
+  </si>
+  <si>
+    <t>Pengekstrakan gejala sistemik yang sangat menyeluruh. 18-21</t>
+  </si>
+  <si>
+    <t>034_c002</t>
+  </si>
+  <si>
+    <t>PENYAKIT: alahan gandum, sindrom rengsa usus, intoleransi laktosa, penyakit seliak. RAWATAN: diet bebas gluten. DIAGNOSIS: ujian darah untuk antibodi IgE tertentu. 22, 23</t>
+  </si>
+  <si>
+    <t>"gluten" (PUNCA). 22</t>
+  </si>
+  <si>
+    <t>diagnoseOleh: alahan gandum -&gt; ujian darah. 22</t>
+  </si>
+  <si>
+    <t>rawatanDgn: intoleransi gluten -&gt; diet bebas gluten. 22</t>
+  </si>
+  <si>
+    <t>Berjaya membezakan antara pelbagai jenis gangguan usus. 22, 23</t>
+  </si>
+  <si>
+    <t>034_c003</t>
+  </si>
+  <si>
+    <t>GEJALA: gejala. DIAGNOSIS: pemeriksaan berkala dengan doktor. 24</t>
+  </si>
+  <si>
+    <t>WRONG LABEL: "badan bertindak balas terhadap gluten" (Dilabel PUNCA, ia adalah huraian proses biologi). 24</t>
+  </si>
+  <si>
+    <t>punca: badan bertindak balas terhadap gluten -&gt; gejala. 24</t>
+  </si>
+  <si>
+    <t>diagnoseOleh: pemeriksaan berkala -&gt; gejala (Ralat: Prosedur mendiagnosis penyakit, bukan gejala). 24</t>
+  </si>
+  <si>
+    <t>Ralat logik hubungan diagnosis dikesan. 23, 24</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>012</t>
-  </si>
-  <si>
-    <t>012_c001</t>
-  </si>
-  <si>
-    <t>PENYAKIT: Glaukoma, diabetes. GEJALA: penglihatan kabur, sakit mata, buta, 'penglihatan terowong'. PUNCA: tekanan cecair yang tinggi, steroid. FAKTOR_RISIKO: umur lanjut.</t>
-  </si>
-  <si>
-    <t>WRONG LABEL: "Saraf optik" (Dilabel PENYAKIT, ia adalah ANATOMI).</t>
-  </si>
-  <si>
-    <t>"titisan mata" (RAWATAN).</t>
-  </si>
-  <si>
-    <t>adaGejala: Glaukoma -&gt; buta, 'penglihatan terowong'. punca: tekanan cecair yang tinggi -&gt; glaukoma.</t>
-  </si>
-  <si>
-    <t>adaRisiko: diabetes -&gt; Glaukoma.</t>
-  </si>
-  <si>
-    <t>Melabel anatomi sebagai penyakit adalah kesilapan struktur yang kerap berlaku dalam model ini. 12</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>025</t>
-  </si>
-  <si>
-    <t>025_c001</t>
-  </si>
-  <si>
-    <t>PENYAKIT: kaki atlet, jangkitan kulat. GEJALA: sisik antara jari kaki, retakan yang menyakitkan, penebalan tapak kaki, lepuh, kudis terbuka (ulser). PUNCA: jangkitan kulat.</t>
-  </si>
-  <si>
-    <t>"Tinea pedis" (PENYAKIT).</t>
-  </si>
-  <si>
-    <t>adaGejala: kaki atlet -&gt; sisik, retakan, penebalan. adaRisiko: kaki yang basah, kasut tertutup -&gt; kaki atlet. punca: jangkitan kulat -&gt; kaki atlet.</t>
-  </si>
-  <si>
-    <t>Chunk ini diekstrak dengan ketepatan hampir sempurna. 13, 14, 15</t>
-  </si>
-  <si>
-    <t>025_c002</t>
-  </si>
-  <si>
-    <t>PENYAKIT: kaki atlet. RAWATAN: azoles, allylamines, ciclopirox, butenafine, fluconazole, terbinafine, ubat antikulat oral.</t>
-  </si>
-  <si>
-    <t>"jangkitan kulat" (PENYAKIT).</t>
-  </si>
-  <si>
-    <t>rawatanDgn: kaki atlet -&gt; azoles, ciclopirox, terbinafine, ubat antikulat oral.</t>
-  </si>
-  <si>
-    <t>Pengekstrakan ubat-ubatan farmakologi sangat lengkap. 16</t>
-  </si>
-  <si>
-    <t>025_c003</t>
-  </si>
-  <si>
-    <t>PENYAKIT: jangkitan. RAWATAN: ubat yang ditetapkan. PENCEGAHAN: mengeringkan kaki, Elakkan memakai kasut tertutup.</t>
-  </si>
-  <si>
-    <t>"nilon" (FAKTOR_RISIKO).</t>
-  </si>
-  <si>
-    <t>pencegahanOleh: jangkitan -&gt; mengeringkan kaki, Elakkan kasut tertutup. rawatanDgn: jangkitan -&gt; ubat yang ditetapkan.</t>
-  </si>
-  <si>
-    <t>Mengaitkan langkah pencegahan dengan jangkitan secara tepat. 17, 18</t>
-  </si>
-  <si>
-    <t>034</t>
-  </si>
-  <si>
-    <t>034_c001</t>
-  </si>
-  <si>
-    <t>PENYAKIT: penyakit seliak, CD. GEJALA: kembung perut, cirit-birit, sembelit, hilang berat badan, anemia, kabut otak. PUNCA: kecenderungan genetik, gluten. DIAGNOSIS: ujian darah, biopsi usus kecil.</t>
-  </si>
-  <si>
-    <t>"protein khusus" (PUNCA).</t>
-  </si>
-  <si>
-    <t>adaGejala: penyakit seliak -&gt; ketidakselesaan perut, sembelit, anemia, kabut otak. punca: kecenderungan genetik, gluten -&gt; penyakit seliak.</t>
-  </si>
-  <si>
-    <t>diagnoseOleh: penyakit seliak -&gt; biopsi usus kecil.</t>
-  </si>
-  <si>
-    <t>Sangat komprehensif dalam menyenaraikan gejala sistemik. 19, 20, 21, 22</t>
-  </si>
-  <si>
-    <t>034_c002</t>
-  </si>
-  <si>
-    <t>PENYAKIT: alahan gandum, sindrom rengsa usus, intoleransi laktosa, penyakit seliak. RAWATAN: diet bebas gluten. DIAGNOSIS: ujian darah untuk antibodi IgE tertentu.</t>
-  </si>
-  <si>
-    <t>"gluten" (PUNCA).</t>
-  </si>
-  <si>
-    <t>diagnoseOleh: alahan gandum -&gt; ujian darah. rawatanDgn: intoleransi gluten -&gt; diet bebas gluten.</t>
-  </si>
-  <si>
-    <t>Membezakan antara pelbagai penyakit usus dengan baik. 23, 24</t>
-  </si>
-  <si>
-    <t>034_c003</t>
-  </si>
-  <si>
-    <t>GEJALA: gejala. DIAGNOSIS: pemeriksaan berkala dengan doktor.</t>
-  </si>
-  <si>
-    <t>WRONG LABEL: "badan bertindak balas terhadap gluten" (Dilabel PUNCA, ia adalah mekanisme biologi).</t>
-  </si>
-  <si>
-    <t>punca: badan bertindak balas terhadap gluten -&gt; gejala.</t>
-  </si>
-  <si>
-    <t>WRONG RELATION: pemeriksaan berkala -&gt; diagnoseOleh -&gt; gejala (Ralat: Prosedur mendiagnosis penyakit, bukan gejala).</t>
-  </si>
-  <si>
-    <t>Ralat logik hubungan antara diagnosis dan gejala. 24, 25</t>
-  </si>
-  <si>
     <t>068</t>
   </si>
   <si>
     <t>068_c001</t>
   </si>
   <si>
-    <t>PENYAKIT: Anemia kekurangan zat besi. GEJALA: Rasa lemah, Kelesuan, Meragam, Kuku rapuh, Sakit lidah, Sindrom kaki resah. PUNCA: kekurangan zat besi, Diet rendah zat besi.</t>
-  </si>
-  <si>
-    <t>WRONG ENTITY: "Pica (keinginan yang tidak tipikal...)" (Dilabel GEJALA tetapi menyertakan seluruh definisi dalam entiti).</t>
-  </si>
-  <si>
-    <t>"tisu" (ANATOMI).</t>
-  </si>
-  <si>
-    <t>adaGejala: Anemia -&gt; Kelesuan, Meragam, Kuku rapuh. punca: kekurangan zat besi -&gt; Anemia.</t>
-  </si>
-  <si>
-    <t>adaRisiko: vegetarian atau vegan -&gt; Anemia.</t>
-  </si>
-  <si>
-    <t>Entiti tidak bersih kerana mengandungi huraian ayat. 26, 27, 28</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>110_c001</t>
-  </si>
-  <si>
-    <t>PENYAKIT: artritis, Osteoartritis (OA), Artritis Reumatoid (RA). GEJALA: bengkak, kekakuan, kehangatan. PUNCA: 'haus-dan-koyak', sistem imun menyerang sel sihat.</t>
-  </si>
-  <si>
-    <t>"rawan pelindung" (ANATOMI).</t>
-  </si>
-  <si>
-    <t>punca: 'haus-dan-koyak' -&gt; OA; sistem imun menyerang -&gt; RA. adaGejala: OA, RA -&gt; sakit sendi, bengkak.</t>
-  </si>
-  <si>
-    <t>Membezakan etiologi OA dan RA dengan sangat tepat. 29, 30, 31</t>
-  </si>
-  <si>
-    <t>110_c002</t>
-  </si>
-  <si>
-    <t>PENYAKIT: artritis. FAKTOR_RISIKO: Umur, Jantina, Merokok, obes, jangkitan, Postur yang lemah. DIAGNOSIS: sejarah perubatan, pemeriksaan fizikal, ujian darah, X-ray, MRI. RAWATAN: NSAID, Steroid, DMARD.</t>
-  </si>
-  <si>
-    <t>"urinalisis" (DIAGNOSIS).</t>
-  </si>
-  <si>
-    <t>adaRisiko: Umur, Merokok, obes -&gt; artritis. diagnoseOleh: artritis -&gt; pemeriksaan fizikal, X-ray, MRI. rawatanDgn: RA -&gt; DMARD.</t>
-  </si>
-  <si>
-    <t>diagnoseOleh: artritis -&gt; analisis cecair sendi.</t>
-  </si>
-  <si>
-    <t>Senarai faktor risiko sangat lengkap. 32, 33, 34, 35, 36</t>
-  </si>
-  <si>
-    <t>110_c003</t>
-  </si>
-  <si>
-    <t>PENYAKIT: Artritis rheumatoid, anemia, strok, kanser. RAWATAN: Terapi fizikal, Pembedahan.</t>
-  </si>
-  <si>
-    <t>"fibrosis paru-paru" (PENYAKIT).</t>
-  </si>
-  <si>
-    <t>rawatanDgn: Artritis rheumatoid -&gt; Terapi fizikal, Pembedahan.</t>
-  </si>
-  <si>
-    <t>adaRisiko: Artritis rheumatoid -&gt; anemia, strok, kanser.</t>
-  </si>
-  <si>
-    <t>Menghubungkan rawatan fizikal dan komplikasi sistemik. 37</t>
+    <t>PENYAKIT: Anemia kekurangan zat besi. GEJALA: Rasa lemah, Kelesuan, Meragam, Kuku rapuh, Sakit lidah, Sindrom kaki resah. PUNCA: kekurangan zat besi, Diet rendah zat besi, Penyerapan zat besi yang lemah. 25-27</t>
+  </si>
+  <si>
+    <t>WRONG ENTITY: "Pica (keinginan yang tidak tipikal...)" (Dilabel GEJALA tetapi menyertakan seluruh ayat definisi dalam entiti). 26</t>
+  </si>
+  <si>
+    <t>"tisu" (Anatomi). 25</t>
+  </si>
+  <si>
+    <t>adaGejala: Anemia -&gt; Kelesuan, Meragam, Sakit lidah, dll. punca: kekurangan zat besi, Diet rendah zat besi -&gt; Anemia. 25-27</t>
+  </si>
+  <si>
+    <t>adaRisiko: vegetarian atau vegan -&gt; Anemia. 27</t>
+  </si>
+  <si>
+    <t>Entiti tidak bersih kerana mengandungi teks huraian definisi. 25-27</t>
+  </si>
+  <si>
+    <t>068_c002</t>
+  </si>
+  <si>
+    <t>PENYAKIT: anemia. PUNCA: kehamilan, haid yang berat, pendarahan gastrousus, ulser peptik, kanser kolorektal. DIAGNOSIS: CBC, Hemoglobin (Hb), Serum feritin, TIBC, Endoskopi. 28-30</t>
+  </si>
+  <si>
+    <t>"wanita hamil" (FAKTOR_RISIKO). 28</t>
+  </si>
+  <si>
+    <t>adaRisiko: wanita hamil -&gt; anemia. diagnoseOleh: anemia -&gt; CBC, Hb, RBC, Serum feritin, TIBC, dll. punca: haid berat, pendarahan gastrousus -&gt; anemia. 28-31</t>
+  </si>
+  <si>
+    <t>diagnoseOleh: pendarahan gastrousus -&gt; Endoskopi. 30</t>
+  </si>
+  <si>
+    <t>Sangat lengkap dalam parameter diagnostik hematologi. 28-31</t>
+  </si>
+  <si>
+    <t>068_c003</t>
+  </si>
+  <si>
+    <t>PENYAKIT: anemia kekurangan zat besi. DIAGNOSIS: kolonoskopi, pemeriksaan penyakit celiac, Biopsi sumsum tulang. RAWATAN: menangani punca asas. 31</t>
+  </si>
+  <si>
+    <t>diagnoseOleh: anemia -&gt; kolonoskopi, biopsi sumsum. rawatanDgn: anemia -&gt; menangani punca. 31</t>
+  </si>
+  <si>
+    <t>Tepat. 31</t>
+  </si>
+  <si>
+    <t>068_c004</t>
+  </si>
+  <si>
+    <t>PENYAKIT: anemia. GEJALA: sembelit, cirit-birit, sakit perut, pedih ulu hati, loya/muntah, najis lebih gelap. RAWATAN: suplemen zat besi oral. 32-34</t>
+  </si>
+  <si>
+    <t>"penyakit buah pinggang kronik" (PENYAKIT). 32</t>
+  </si>
+  <si>
+    <t>rawatanDgn: anemia, kekurangan zat besi -&gt; suplemen. adaGejala: anemia -&gt; sembelit, sakit perut, najis gelap, dll. 32-34</t>
+  </si>
+  <si>
+    <t>rawatanDgn: penyakit buah pinggang -&gt; merawat pendarahan. 32</t>
+  </si>
+  <si>
+    <t>Hubungan kesan sampingan rawatan dikesan dengan baik. 32-34</t>
+  </si>
+  <si>
+    <t>068_c005</t>
+  </si>
+  <si>
+    <t>PENYAKIT: anemia. GEJALA: keletihan, sakit dada, sesak nafas. RAWATAN: pemindahan darah. DIAGNOSIS: ujian darah susulan, paras haemoglobin, feritin. 34, 35</t>
+  </si>
+  <si>
+    <t>adaGejala: anemia -&gt; keletihan, sakit dada, sesak nafas. rawatanDgn: anemia -&gt; pemindahan darah. 35</t>
+  </si>
+  <si>
+    <t>diagnoseOleh: anemia -&gt; ujian darah susulan. 35</t>
+  </si>
+  <si>
+    <t>Tepat. 34, 35</t>
   </si>
   <si>
     <t>182</t>
@@ -382,34 +352,121 @@
     <t>182_c001</t>
   </si>
   <si>
-    <t>PENYAKIT: Kekurangan G6PD. GEJALA: pucat, jaundis, air kencing berwarna gelap, susah bernafas, lesu. PUNCA: kekurangan enzim G6PD. RAWATAN: transfusi. PENCEGAHAN: kacang fava, naftalena, aspirin, dapsone.</t>
-  </si>
-  <si>
-    <t>"sel darah merah" (ANATOMI).</t>
-  </si>
-  <si>
-    <t>adaGejala: G6PD -&gt; pucat, jaundis, air kencing gelap. punca: kekurangan enzim -&gt; G6PD. pencegahanOleh: G6PD -&gt; kacang fava, naftalena, aspirin.</t>
-  </si>
-  <si>
-    <t>INCORRECT: G6PD -&gt; adaGejala -&gt; sawan (Halusinasi/Cross-contamination daripada Artikel 181 - Sawan Demam).</t>
-  </si>
-  <si>
-    <t>pencegahanOleh: G6PD -&gt; antimalaria.</t>
-  </si>
-  <si>
-    <t>Ralat perubatan serius: G6PD tidak menyebabkan sawan; maklumat ditarik dari perenggan lain. 38, 39, 40, 41, 42</t>
+    <t>PENYAKIT: Kekurangan Glukosa-6-fosfat dehidrogenase (G6PD). GEJALA: pucat, jaundis, air kencing berwarna gelap, makan sedikit, susah bernafas, lesu. PUNCA: kekurangan enzim G6PD. RAWATAN: transfusi. PENCEGAHAN: kacang fava, naftalena, aspirin, dapsone. 36-42</t>
+  </si>
+  <si>
+    <t>"sel darah merah" (Anatomi). 36</t>
+  </si>
+  <si>
+    <t>adaGejala: G6PD -&gt; pucat, jaundis, air kencing gelap, lesu. punca: kekurangan enzim -&gt; G6PD. pencegahanOleh: G6PD -&gt; kacang fava, naftalena, aspirin, dapsone. 36-42</t>
+  </si>
+  <si>
+    <t>adaGejala: G6PD -&gt; sawan (HALUSINASI/PENCEMARAN SILANG, teks tidak menyebut sawan bagi G6PD; ia ditarik dari Artikel 181). 38</t>
+  </si>
+  <si>
+    <t>pencegahanOleh: G6PD -&gt; antimalaria, nitrofurantoin. 40, 41</t>
+  </si>
+  <si>
+    <t>Ralat perubatan serius: Memasukkan "sawan" sebagai gejala G6PD adalah ralat konteks. 36-42</t>
   </si>
   <si>
     <t>182_c002</t>
   </si>
   <si>
-    <t>PENYAKIT: Kekurangan G6PD. PENCEGAHAN: mengelakkan perubatan dan makanan tertentu.</t>
-  </si>
-  <si>
-    <t>pencegahanOleh: Kekurangan G6PD -&gt; mengelakkan perubatan dan makanan tertentu.</t>
-  </si>
-  <si>
-    <t>Ringkas dan tepat. 43</t>
+    <t>PENYAKIT: kekurangan G6PD. PENCEGAHAN: mengelakkan perubatan dan makanan tertentu. 42</t>
+  </si>
+  <si>
+    <t>pencegahanOleh: kekurangan G6PD -&gt; mengelakkan perubatan. 42</t>
+  </si>
+  <si>
+    <t>Ringkas dan tepat. 42</t>
+  </si>
+  <si>
+    <t>193</t>
+  </si>
+  <si>
+    <t>193_c001</t>
+  </si>
+  <si>
+    <t>PENYAKIT: kegagalan jantung, kardiomiopati, anemia, diabetes, hipertensi pulmonari. GEJALA: sesak nafas, bengkak, keletihan, batuk berterusan, pening. PUNCA: Penyakit arteri koronari, Tekanan darah tinggi. RAWATAN: ubat, pembedahan pintasan, pemindahan jantung. 43-52</t>
+  </si>
+  <si>
+    <t>WRONG ENTITY: "tekanan intraokular tinggi" (Dilabel PUNCA - HALUSINASI, tidak disebut dalam teks jantung). 45</t>
+  </si>
+  <si>
+    <t>"peptida natriuretik" (DIAGNOSIS). 46</t>
+  </si>
+  <si>
+    <t>adaGejala: kegagalan jantung -&gt; sesak nafas, bengkak, keletihan, dll. punca: Arteri koronari, Kardiomiopati -&gt; kegagalan jantung. diagnoseOleh: kegagalan jantung -&gt; ekokardiogram, ECG, imbasan CT. 43-51</t>
+  </si>
+  <si>
+    <t>punca: tekanan intraokular tinggi -&gt; kegagalan jantung. 45</t>
+  </si>
+  <si>
+    <t>adaRisiko: merokok, obesiti -&gt; kegagalan jantung. 48</t>
+  </si>
+  <si>
+    <t>Halusinasi "tekanan mata" dalam kegagalan jantung merosakkan logik artikel. 43-52</t>
+  </si>
+  <si>
+    <t>193_c002</t>
+  </si>
+  <si>
+    <t>PENYAKIT: tekanan darah tinggi, diabetes. PENCEGAHAN: Kekal aktif secara fizikal, Makan makanan yang sihat, Mengekalkan berat badan yang sihat, Mengurus tekanan. 52-54</t>
+  </si>
+  <si>
+    <t>pencegahanOleh: tekanan darah tinggi, diabetes -&gt; Kekal aktif, Makan sihat, dll. 53, 54</t>
+  </si>
+  <si>
+    <t>Pemetaan langkah pencegahan kepada dua penyakit secara serentak adalah tepat. 52-54</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>238_c001</t>
+  </si>
+  <si>
+    <t>PENYAKIT: gout. GEJALA: sendi yang radang, sakit secara tiba-tiba, bengkak, Kemerahan, Kekakuan sendi. 55, 56</t>
+  </si>
+  <si>
+    <t>WRONG LABEL: "tophi" (Dilabel PUNCA, sepatutnya GEJALA/Komplikasi). 57</t>
+  </si>
+  <si>
+    <t>"kristal urate" (PUNCA). 55</t>
+  </si>
+  <si>
+    <t>punca: pengumpulan asid urik -&gt; gout. adaGejala: gout -&gt; sendi radang, bengkak, kemerahan, dll. adaRisiko: Diet daging/makanan laut -&gt; gout. 55, 56</t>
+  </si>
+  <si>
+    <t>Ralat label PUNCA bagi komplikasi (tophi) dikesan. 55, 56</t>
+  </si>
+  <si>
+    <t>238_c002</t>
+  </si>
+  <si>
+    <t>PENYAKIT: gout, obesiti, tekanan darah tinggi, kencing manis. DIAGNOSIS: pemeriksaan fizikal, Analisis cecair sinovial, ujian asid urik. RAWATAN: ibuprofen, naproxen, indomethacin, Colchicine, Allopurinol, Febuxostat. 58-60</t>
+  </si>
+  <si>
+    <t>adaRisiko: tekanan darah tinggi, diabetes, obesiti -&gt; gout. diagnoseOleh: gout -&gt; pemeriksaan fizikal, analisis cecair. rawatanDgn: gout -&gt; NSAID, ibuprofen, Colchicine, Allopurinol, dll. 58-60</t>
+  </si>
+  <si>
+    <t>Pengekstrakan farmakologi sangat jitu. 58-60</t>
+  </si>
+  <si>
+    <t>238_c003</t>
+  </si>
+  <si>
+    <t>PENYAKIT: gout. RAWATAN: kekal terhidrat. PENCEGAHAN: Kekalkan berat badan yang sihat, Senaman yang kerap, Elakkan makanan kaya purin, Minum lebih banyak air. 57, 61-63</t>
+  </si>
+  <si>
+    <t>WRONG LABEL: "kerosakan sendi kekal", "kerosakan buah pinggang" (Dilabel PUNCA, ia adalah GEJALA/Kesan). 57</t>
+  </si>
+  <si>
+    <t>adaRisiko: berat badan tidak sihat, makanan purin, minuman manis -&gt; gout. pencegahanOleh: gout -&gt; Senaman, Elak purin, Minum air. rawatanDgn: gout -&gt; kekal terhidrat. 61-63</t>
+  </si>
+  <si>
+    <t>Ralat kategori label bagi kesan penyakit sebagai punca. 57, 61-63</t>
   </si>
   <si>
     <t>244</t>
@@ -418,82 +475,79 @@
     <t>244_c001</t>
   </si>
   <si>
-    <t>PENYAKIT: Tuberkulosis, TB, batuk kering.</t>
-  </si>
-  <si>
-    <t>WRONG ENTITY: "tekanan intraokular tinggi" (Dilabel sebagai PUNCA - Halusinasi sistemik).</t>
-  </si>
-  <si>
-    <t>"Mycobacterium tuberculosis" (PUNCA).</t>
-  </si>
-  <si>
-    <t>punca: Mycobacterium tuberculosis -&gt; Tuberkulosis.</t>
-  </si>
-  <si>
-    <t>WRONG RELATION: tekanan intraokular tinggi -&gt; punca -&gt; TB.</t>
-  </si>
-  <si>
-    <t>Terdapat halusinasi "tekanan mata" yang muncul secara rawak dalam etiologi TB. 44</t>
+    <t>PENYAKIT: Tuberkulosis, TB, batuk kering. 64</t>
+  </si>
+  <si>
+    <t>WRONG ENTITY: "tekanan intraokular tinggi" (Dilabel PUNCA - HALUSINASI, tidak disebut dalam teks TB). 64</t>
+  </si>
+  <si>
+    <t>"Mycobacterium tuberculosis" (PUNCA). 64</t>
+  </si>
+  <si>
+    <t>punca: Mycobacterium tuberculosis -&gt; Tuberkulosis, TB, batuk kering. 64</t>
+  </si>
+  <si>
+    <t>punca: tekanan intraokular tinggi -&gt; Tuberkulosis, TB. 64</t>
+  </si>
+  <si>
+    <t>Halusinasi sistemik "tekanan mata" muncul lagi dalam etiologi TB. 64</t>
   </si>
   <si>
     <t>244_c002</t>
   </si>
   <si>
-    <t>PENYAKIT: tuberkulosis, HIV, diabetes mellitus, artritis reumatoid. GEJALA: batuk kering terpendam, Batuk kronik, Batuk berdarah, Berpeluh malam, Hilang berat badan, Lemah.</t>
-  </si>
-  <si>
-    <t>"kekurangan zat makanan" (FAKTOR_RISIKO).</t>
-  </si>
-  <si>
-    <t>punca: Mycobacterium tuberculosis -&gt; tuberkulosis. adaRisiko: HIV, diabetes -&gt; tuberkulosis. adaGejala: tuberkulosis -&gt; Batuk kronik, Berpeluh malam, Hilang berat badan.</t>
-  </si>
-  <si>
-    <t>adaRisiko: ubat imunosupresif -&gt; tuberkulosis.</t>
-  </si>
-  <si>
-    <t>Pengekstrakan risiko bagi pesakit imunokompromi adalah sangat baik. 45, 46, 47</t>
+    <t>PENYAKIT: tuberkulosis, HIV, diabetes mellitus, artritis reumatoid. GEJALA: batuk kering terpendam, Batuk kronik, Batuk berdarah, Berpeluh malam, Hilang berat badan, Lemah atau lesu. 65-67</t>
+  </si>
+  <si>
+    <t>"kekurangan zat makanan" (FAKTOR_RISIKO). 65</t>
+  </si>
+  <si>
+    <t>punca: Mycobacterium tuberculosis -&gt; tuberkulosis. adaGejala: tuberkulosis -&gt; batuk kronik, Berpeluh malam, Hilang berat badan, dll. adaRisiko: HIV, diabetes, ubat imunosupresif -&gt; tuberkulosis. 65-67</t>
+  </si>
+  <si>
+    <t>Pengekstrakan risiko bagi pesakit imunokompromi adalah sangat baik. 65-67</t>
   </si>
   <si>
     <t>244_c003</t>
   </si>
   <si>
-    <t>PENYAKIT: tuberkulosis, jangkitan tuberkulosis. RAWATAN: Rifampin, Isoniazid, rifapentine, Ethambutol (EMB), Pyrazinamide (PZA), Rifampicin (RIF). DIAGNOSIS: kultur positif.</t>
-  </si>
-  <si>
-    <t>diagnoseOleh: tuberkulosis -&gt; kultur positif. rawatanDgn: tuberkulosis, jangkitan -&gt; Rifampin, Isoniazid, EMB, PZA.</t>
-  </si>
-  <si>
-    <t>Ketepatan tinggi dalam singkatan perubatan (EMB, PZA, RIF). 48, 49</t>
+    <t>PENYAKIT: tuberkulosis, jangkitan tuberkulosis. DIAGNOSIS: kultur positif. RAWATAN: Rifampin, Isoniazid, rifapentine, EMB, PZA, RIF. 68, 69</t>
+  </si>
+  <si>
+    <t>diagnoseOleh: tuberkulosis -&gt; kultur positif. rawatanDgn: tuberkulosis, jangkitan -&gt; Rifampin, Isoniazid, EMB, PZA, RIF. 68, 69</t>
+  </si>
+  <si>
+    <t>Ketepatan tinggi dalam singkatan ubat perubatan. 68, 69</t>
   </si>
   <si>
     <t>244_c004</t>
   </si>
   <si>
-    <t>PENYAKIT: tuberkulosis, HIV. GEJALA: batuk berterusan, demam, penurunan berat badan. RAWATAN: ubat anti-tuberkulosis, DOT, VOT. PENCEGAHAN: pengesanan dan rawatan peringkat awal, jaga kebersihan.</t>
-  </si>
-  <si>
-    <t>"vaksin BCG" (PENCEGAHAN).</t>
-  </si>
-  <si>
-    <t>adaGejala: tuberkulosis -&gt; batuk, demam, penurunan berat badan. rawatanDgn: tuberkulosis -&gt; DOT, VOT. pencegahanOleh: tuberkulosis -&gt; rawatan peringkat awal.</t>
-  </si>
-  <si>
-    <t>pencegahanOleh: tuberkulosis -&gt; vaksin BCG.</t>
-  </si>
-  <si>
-    <t>Mengenalpasti program rawatan (DOT/VOT) dengan tepat. 50, 51, 52</t>
+    <t>PENYAKIT: tuberkulosis, HIV. GEJALA: batuk berterusan, demam, penurunan berat badan. RAWATAN: ubat anti-tuberkulosis, DOT, VOT. PENCEGAHAN: pengesanan dan rawatan peringkat awal, jaga kebersihan. 70-72</t>
+  </si>
+  <si>
+    <t>"vaksinasi Vaksin BCG" (PENCEGAHAN). 71</t>
+  </si>
+  <si>
+    <t>adaGejala: tuberkulosis -&gt; batuk, demam, penurunan berat badan. rawatanDgn: tuberkulosis -&gt; DOT, VOT, ubat anti-TB. pencegahanOleh: tuberkulosis -&gt; rawatan peringkat awal. 71, 72</t>
+  </si>
+  <si>
+    <t>pencegahanOleh: tuberkulosis -&gt; lengkapkan rawatan. 72</t>
+  </si>
+  <si>
+    <t>Mengenalpasti program kesihatan awam (DOT/VOT) dengan tepat. 70-72</t>
   </si>
   <si>
     <t>244_c005</t>
   </si>
   <si>
-    <t>PENYAKIT: tuberkulosis. PENCEGAHAN: vaksin BCG, imunisasi baru lahir.</t>
-  </si>
-  <si>
-    <t>pencegahanOleh: tuberkulosis -&gt; vaksin BCG, imunisasi baru lahir.</t>
-  </si>
-  <si>
-    <t>Tepat. 53</t>
+    <t>PENYAKIT: tuberkulosis. PENCEGAHAN: vaksin BCG, imunisasi baru lahir rutin. 73</t>
+  </si>
+  <si>
+    <t>pencegahanOleh: tuberkulosis -&gt; vaksin BCG, imunisasi baru lahir. 73</t>
+  </si>
+  <si>
+    <t>Tepat. 73</t>
   </si>
 </sst>
 </file>
@@ -752,12 +806,13 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="7.75"/>
     <col customWidth="1" min="2" max="2" width="8.38"/>
-    <col customWidth="1" min="3" max="3" width="214.13"/>
-    <col customWidth="1" min="4" max="4" width="96.88"/>
-    <col customWidth="1" min="5" max="5" width="36.13"/>
-    <col customWidth="1" min="6" max="6" width="187.63"/>
-    <col customWidth="1" min="7" max="7" width="93.63"/>
-    <col customWidth="1" min="8" max="8" width="48.5"/>
+    <col customWidth="1" min="3" max="3" width="244.25"/>
+    <col customWidth="1" min="4" max="4" width="103.0"/>
+    <col customWidth="1" min="5" max="5" width="41.0"/>
+    <col customWidth="1" min="6" max="6" width="205.63"/>
+    <col customWidth="1" min="7" max="7" width="161.38"/>
+    <col customWidth="1" min="8" max="8" width="49.63"/>
+    <col customWidth="1" min="9" max="9" width="71.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -844,16 +899,16 @@
         <v>25</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -861,28 +916,28 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>19</v>
@@ -890,551 +945,551 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>106</v>
+        <v>35</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>16</v>
+        <v>116</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>16</v>
+        <v>126</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>145</v>
+        <v>35</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>146</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>147</v>
@@ -1443,89 +1498,185 @@
         <v>148</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>16</v>
+        <v>149</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>16</v>
+        <v>155</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>16</v>
+        <v>158</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>155</v>
+        <v>35</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>16</v>
+        <v>162</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
